--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 6 - КДР/ОБЩИНА ВАРНА % 6 - КДР.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 6 - КДР/ОБЩИНА ВАРНА % 6 - КДР.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="49">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -61,21 +64,24 @@
     <t>2026-08-03</t>
   </si>
   <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>Варна Евkсиноград</t>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
   </si>
   <si>
     <t>КДР6</t>
   </si>
   <si>
+    <t>КДР3</t>
+  </si>
+  <si>
     <t>КДР2</t>
   </si>
   <si>
-    <t>КДР3</t>
-  </si>
-  <si>
     <t>КДР4</t>
   </si>
   <si>
@@ -85,12 +91,12 @@
     <t>78970155027722945</t>
   </si>
   <si>
+    <t>78970155027722911</t>
+  </si>
+  <si>
     <t>78970155027722903</t>
   </si>
   <si>
-    <t>78970155027722911</t>
-  </si>
-  <si>
     <t>78970155027722929</t>
   </si>
   <si>
@@ -100,19 +106,43 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>08:32</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>18:35</t>
-  </si>
-  <si>
-    <t>18:54</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>08:31:00</t>
+  </si>
+  <si>
+    <t>18:30:00</t>
+  </si>
+  <si>
+    <t>18:25:00</t>
+  </si>
+  <si>
+    <t>18:35:00</t>
+  </si>
+  <si>
+    <t>18:54:00</t>
+  </si>
+  <si>
+    <t>16:41:00</t>
+  </si>
+  <si>
+    <t>3235669065 3235669065</t>
+  </si>
+  <si>
+    <t>3235797875 3235797875</t>
+  </si>
+  <si>
+    <t>3235800590 3235800590</t>
+  </si>
+  <si>
+    <t>3235801195 3235801195</t>
+  </si>
+  <si>
+    <t>3235803337 3235803337</t>
+  </si>
+  <si>
+    <t>3236571703 3236571703</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА ВАРНА % 6 - КДР</t>
@@ -137,9 +167,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00000"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -219,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -232,10 +263,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -530,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -539,16 +572,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -588,283 +622,345 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2">
+        <v>40.44</v>
+      </c>
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1.659</v>
+      </c>
+      <c r="I2" s="1">
+        <v>67.09</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1.77</v>
+      </c>
+      <c r="K2" s="1">
+        <v>71.57899999999999</v>
+      </c>
+      <c r="L2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2">
-        <v>40.441</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="H2">
-        <v>70.367</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="J2">
-        <v>71.581</v>
-      </c>
-      <c r="K2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>139150</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F3">
         <v>66.48</v>
       </c>
-      <c r="G3" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="H3">
-        <v>117.005</v>
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1.669</v>
       </c>
       <c r="I3" s="1">
+        <v>110.955</v>
+      </c>
+      <c r="J3" s="1">
         <v>1.79</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>118.999</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
         <v>29</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>136140</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
       </c>
       <c r="F4">
         <v>66.48</v>
       </c>
-      <c r="G4" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="H4">
-        <v>117.005</v>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1.669</v>
       </c>
       <c r="I4" s="1">
+        <v>110.955</v>
+      </c>
+      <c r="J4" s="1">
         <v>1.79</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>118.999</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5">
+        <v>66.42</v>
+      </c>
+      <c r="G5" t="s">
         <v>30</v>
       </c>
-      <c r="L4">
+      <c r="H5" s="1">
+        <v>1.669</v>
+      </c>
+      <c r="I5" s="1">
+        <v>110.855</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1.79</v>
+      </c>
+      <c r="K5" s="1">
+        <v>118.892</v>
+      </c>
+      <c r="L5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="M4">
-        <v>136143</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5">
-        <v>66.419</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="H5">
-        <v>116.897</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="J5">
-        <v>118.89</v>
-      </c>
-      <c r="K5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>136148</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F6">
         <v>66.48</v>
       </c>
-      <c r="G6" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="H6">
-        <v>117.005</v>
+      <c r="G6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1.669</v>
       </c>
       <c r="I6" s="1">
+        <v>110.955</v>
+      </c>
+      <c r="J6" s="1">
         <v>1.79</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>118.999</v>
       </c>
-      <c r="K6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6">
+      <c r="L6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="M6">
-        <v>136170</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="N6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7">
+        <v>26.67</v>
+      </c>
+      <c r="G7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1.677</v>
+      </c>
+      <c r="I7" s="1">
+        <v>44.726</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="K7" s="1">
+        <v>48.006</v>
+      </c>
+      <c r="L7" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="6">
-        <v>306.3</v>
-      </c>
-      <c r="C11" s="6">
-        <v>5</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.75736</v>
-      </c>
-      <c r="E11" s="6">
-        <v>538.28</v>
-      </c>
-      <c r="F11" s="6">
-        <v>547.468</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="9">
-        <v>306.3</v>
-      </c>
-      <c r="C12" s="9">
-        <v>5</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="9">
-        <v>538.28</v>
-      </c>
-      <c r="F12" s="9">
-        <v>547.468</v>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="6">
+        <v>332.97</v>
+      </c>
+      <c r="C12" s="7">
+        <v>6</v>
+      </c>
+      <c r="D12" s="8">
+        <v>1.66843</v>
+      </c>
+      <c r="E12" s="6">
+        <v>555.54</v>
+      </c>
+      <c r="F12" s="6">
+        <v>595.47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="10">
+        <v>332.97</v>
+      </c>
+      <c r="C13" s="11">
+        <v>6</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="10">
+        <v>555.54</v>
+      </c>
+      <c r="F13" s="10">
+        <v>595.47</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 6 - КДР/ОБЩИНА ВАРНА % 6 - КДР.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 6 - КДР/ОБЩИНА ВАРНА % 6 - КДР.xlsx
@@ -649,10 +649,10 @@
         <v>30</v>
       </c>
       <c r="H2" s="1">
-        <v>1.659</v>
+        <v>1.74</v>
       </c>
       <c r="I2" s="1">
-        <v>67.09</v>
+        <v>70.366</v>
       </c>
       <c r="J2" s="1">
         <v>1.77</v>
@@ -693,10 +693,10 @@
         <v>30</v>
       </c>
       <c r="H3" s="1">
-        <v>1.669</v>
+        <v>1.76</v>
       </c>
       <c r="I3" s="1">
-        <v>110.955</v>
+        <v>117.005</v>
       </c>
       <c r="J3" s="1">
         <v>1.79</v>
@@ -737,10 +737,10 @@
         <v>30</v>
       </c>
       <c r="H4" s="1">
-        <v>1.669</v>
+        <v>1.76</v>
       </c>
       <c r="I4" s="1">
-        <v>110.955</v>
+        <v>117.005</v>
       </c>
       <c r="J4" s="1">
         <v>1.79</v>
@@ -781,10 +781,10 @@
         <v>30</v>
       </c>
       <c r="H5" s="1">
-        <v>1.669</v>
+        <v>1.76</v>
       </c>
       <c r="I5" s="1">
-        <v>110.855</v>
+        <v>116.899</v>
       </c>
       <c r="J5" s="1">
         <v>1.79</v>
@@ -825,10 +825,10 @@
         <v>30</v>
       </c>
       <c r="H6" s="1">
-        <v>1.669</v>
+        <v>1.76</v>
       </c>
       <c r="I6" s="1">
-        <v>110.955</v>
+        <v>117.005</v>
       </c>
       <c r="J6" s="1">
         <v>1.79</v>
@@ -869,10 +869,10 @@
         <v>30</v>
       </c>
       <c r="H7" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I7" s="1">
-        <v>44.726</v>
+        <v>47.206</v>
       </c>
       <c r="J7" s="1">
         <v>1.8</v>
@@ -931,10 +931,10 @@
         <v>6</v>
       </c>
       <c r="D12" s="8">
-        <v>1.66843</v>
+        <v>1.75837</v>
       </c>
       <c r="E12" s="6">
-        <v>555.54</v>
+        <v>585.49</v>
       </c>
       <c r="F12" s="6">
         <v>595.47</v>
@@ -952,7 +952,7 @@
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="10">
-        <v>555.54</v>
+        <v>585.49</v>
       </c>
       <c r="F13" s="10">
         <v>595.47</v>
